--- a/SGC-CKN/Excel/04ff0a1c-98e5-4b51-b87a-77075e55effb_Lô_CT-02_P8_22_D800_08-04-2026.xlsx
+++ b/SGC-CKN/Excel/04ff0a1c-98e5-4b51-b87a-77075e55effb_Lô_CT-02_P8_22_D800_08-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="71">
   <si>
     <t>Dự án</t>
   </si>
@@ -145,7 +145,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">00:00
+    <t xml:space="preserve">01:00
 08/04/2026</t>
   </si>
   <si>
@@ -189,14 +189,22 @@
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
+    <t xml:space="preserve">04:35
+07/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05:40
+07/04/2026</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Cuội đa màu sắc TT rất chặt</t>
+  </si>
+  <si>
     <t xml:space="preserve">05:40
 08/04/2026</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">06:20
@@ -1353,13 +1361,13 @@
         <v>-26.57</v>
       </c>
       <c r="H15" s="19">
-        <v>1.83</v>
+        <v>0.83</v>
       </c>
       <c r="I15" s="19">
         <v>5.03</v>
       </c>
-      <c r="J15" s="12">
-        <v>2.74</v>
+      <c r="J15" s="8">
+        <v>6.04</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1481,10 +1489,10 @@
         <v>54</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="31">
         <v>-40</v>
@@ -1507,19 +1515,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F20" s="34">
         <v>-43.6</v>
@@ -1542,7 +1550,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1648,31 +1656,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1811,13 +1819,13 @@
         <v>-26.57</v>
       </c>
       <c r="G6" s="19">
-        <v>1.83</v>
+        <v>0.83</v>
       </c>
       <c r="H6" s="19">
         <v>5.03</v>
       </c>
-      <c r="I6" s="12">
-        <v>2.74</v>
+      <c r="I6" s="8">
+        <v>6.04</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1944,7 +1952,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1967,7 +1975,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -1985,13 +1993,13 @@
         <v>-44.65</v>
       </c>
       <c r="G12" s="39">
-        <v>9.83</v>
+        <v>8.83</v>
       </c>
       <c r="H12" s="39">
         <v>43.78</v>
       </c>
       <c r="I12" s="39">
-        <v>4.45</v>
+        <v>4.96</v>
       </c>
     </row>
   </sheetData>
